--- a/dados/banco_dados.xlsx
+++ b/dados/banco_dados.xlsx
@@ -335,8 +335,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tb_oferta" displayName="tb_oferta" ref="A3:I203" headerRowCount="1">
-  <autoFilter ref="A3:I203"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tb_oferta" displayName="tb_oferta" ref="A3:I246" headerRowCount="1">
+  <autoFilter ref="A3:I246"/>
   <tableColumns count="9">
     <tableColumn id="1" name="id_oferta"/>
     <tableColumn id="2" name="id_produto"/>
@@ -661,7 +661,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Modelo estrela do pipeline de preços · atualizado em 17/10/2026 12:04</t>
+          <t>Modelo estrela do pipeline de preços · atualizado em 18/10/2026 13:05</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I203"/>
+  <dimension ref="A1:I246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8332,6 +8332,1425 @@
       </c>
       <c r="I203" s="34" t="n">
         <v>46312.50273148148</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="22" t="n">
+        <v>201</v>
+      </c>
+      <c r="B204" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C204" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" s="29" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="E204" s="29" t="n">
+        <v>1139.15</v>
+      </c>
+      <c r="F204" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G204" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H204" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/320797/processador-amd-ryzen-7-5700x-3-4ghz-4-6ghz-max-turbo-cache-36mb-8-nucleos-16-threads-am4-sem-video-integrado-100-100000926wof</t>
+        </is>
+      </c>
+      <c r="I204" s="31" t="n">
+        <v>46313.53577546297</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="24" t="n">
+        <v>202</v>
+      </c>
+      <c r="B205" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C205" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D205" s="32" t="n">
+        <v>1549.99</v>
+      </c>
+      <c r="E205" s="32" t="n">
+        <v>1059.99</v>
+      </c>
+      <c r="F205" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G205" s="25" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H205" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/405799/processador-amd-ryzen-5-7600-3-8ghz-5-1ghz-max-turbo-cache-38mb-6-nucleos-12-threads-am5-com-video-integrado-100-100001015box</t>
+        </is>
+      </c>
+      <c r="I205" s="34" t="n">
+        <v>46313.53582175926</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="22" t="n">
+        <v>203</v>
+      </c>
+      <c r="B206" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C206" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" s="29" t="n">
+        <v>1978.9</v>
+      </c>
+      <c r="E206" s="29" t="n">
+        <v>1957.56</v>
+      </c>
+      <c r="F206" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G206" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H206" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/466557/processador-amd-ryzen-7-7800x3d-4-2ghz-5-0ghz-max-turbo-cache-104mb-am5-c-video-e-sem-cooler-100-100000910wof</t>
+        </is>
+      </c>
+      <c r="I206" s="31" t="n">
+        <v>46313.53585648148</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="24" t="n">
+        <v>204</v>
+      </c>
+      <c r="B207" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C207" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" s="32" t="n">
+        <v>859.99</v>
+      </c>
+      <c r="E207" s="32" t="n">
+        <v>960.67</v>
+      </c>
+      <c r="F207" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G207" s="25" t="inlineStr">
+        <is>
+          <t>Boa compra</t>
+        </is>
+      </c>
+      <c r="H207" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/283718/processador-intel-core-i5-12400f-2-5ghz-4-4ghz-max-turbo-cache-18mb-6-nucleos-12-threads-lga-1700-sem-video-integrado-bx8071512400f</t>
+        </is>
+      </c>
+      <c r="I207" s="34" t="n">
+        <v>46313.53587962963</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="22" t="n">
+        <v>205</v>
+      </c>
+      <c r="B208" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C208" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" s="29" t="n">
+        <v>1069.99</v>
+      </c>
+      <c r="E208" s="29" t="n">
+        <v>1032.99</v>
+      </c>
+      <c r="F208" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G208" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H208" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/531209/processador-intel-core-i5-14400f-14-geracao-3-5-ghz-4-7-ghz-turbo-cache-20mb-10-nucleos-16-threads-lga1700-sem-video-integrado-bx8071514400f</t>
+        </is>
+      </c>
+      <c r="I208" s="31" t="n">
+        <v>46313.53591435185</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="24" t="n">
+        <v>206</v>
+      </c>
+      <c r="B209" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C209" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" s="32" t="n">
+        <v>2899.9</v>
+      </c>
+      <c r="E209" s="32" t="n">
+        <v>2799.97</v>
+      </c>
+      <c r="F209" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G209" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H209" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/903752/gpu-inno3d-geforce-rtx-5060-twin-x2-8gb-128bits-gddr7-n50602-08d7-195071n</t>
+        </is>
+      </c>
+      <c r="I209" s="34" t="n">
+        <v>46313.5359375</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="22" t="n">
+        <v>207</v>
+      </c>
+      <c r="B210" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C210" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" s="29" t="n">
+        <v>5499.99</v>
+      </c>
+      <c r="E210" s="29" t="n">
+        <v>5437.77</v>
+      </c>
+      <c r="F210" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G210" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H210" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/989623/placa-de-video-palit-rtx-5070-infinity-3-nvidia-geforce-12gb-gddr7-192bit-3-dp-e-hdmi-ne75070019k9-gb2050s</t>
+        </is>
+      </c>
+      <c r="I210" s="31" t="n">
+        <v>46313.53597222222</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="24" t="n">
+        <v>208</v>
+      </c>
+      <c r="B211" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="C211" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" s="32" t="n">
+        <v>2199.99</v>
+      </c>
+      <c r="E211" s="32" t="n">
+        <v>2321.34</v>
+      </c>
+      <c r="F211" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G211" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H211" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/996572/placa-de-video-husky-alpha-rtx-3060-nvidia-12gb-gddr6-192-bit-dual-fan-hdmi-3x-displayport-hvg023060</t>
+        </is>
+      </c>
+      <c r="I211" s="34" t="n">
+        <v>46313.53600694444</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="22" t="n">
+        <v>209</v>
+      </c>
+      <c r="B212" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C212" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" s="29" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="E212" s="29" t="n">
+        <v>1964.96</v>
+      </c>
+      <c r="F212" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G212" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H212" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/459144/placa-de-video-rx-7600-challenger-asrock-amd-radeon-8gb-gddr6-90-ga41zz-00uanf</t>
+        </is>
+      </c>
+      <c r="I212" s="31" t="n">
+        <v>46313.53603009259</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="24" t="n">
+        <v>210</v>
+      </c>
+      <c r="B213" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C213" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" s="32" t="n">
+        <v>519.99</v>
+      </c>
+      <c r="E213" s="32" t="n">
+        <v>562.2</v>
+      </c>
+      <c r="F213" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G213" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H213" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/313833/memoria-kingston-fury-beast-8gb-3200mhz-ddr4-cl16-preto-kf432c16bb-8</t>
+        </is>
+      </c>
+      <c r="I213" s="34" t="n">
+        <v>46313.53606481481</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="22" t="n">
+        <v>211</v>
+      </c>
+      <c r="B214" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C214" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" s="29" t="n">
+        <v>929.99</v>
+      </c>
+      <c r="E214" s="29" t="n">
+        <v>1041.41</v>
+      </c>
+      <c r="F214" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G214" s="23" t="inlineStr">
+        <is>
+          <t>Boa compra</t>
+        </is>
+      </c>
+      <c r="H214" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/172366/memoria-ram-kingston-fury-beast-16gb-3200mhz-ddr4-cl16-preto-kf432c16bb1-16</t>
+        </is>
+      </c>
+      <c r="I214" s="31" t="n">
+        <v>46313.53609953704</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="24" t="n">
+        <v>212</v>
+      </c>
+      <c r="B215" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="C215" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" s="32" t="n">
+        <v>2049.99</v>
+      </c>
+      <c r="E215" s="32" t="n">
+        <v>2126.87</v>
+      </c>
+      <c r="F215" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G215" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H215" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/285967/memoria-ram-kingston-fury-beast-16gb-5600mhz-ddr5-cl40-para-intel-xmp-preto-kf556c40bb-16</t>
+        </is>
+      </c>
+      <c r="I215" s="34" t="n">
+        <v>46313.53612268518</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="22" t="n">
+        <v>213</v>
+      </c>
+      <c r="B216" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="C216" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" s="29" t="n">
+        <v>1139.05</v>
+      </c>
+      <c r="E216" s="29" t="n">
+        <v>1055.21</v>
+      </c>
+      <c r="F216" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G216" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H216" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/1021928/ssd-kingston-nv3-1tb-m-2-2280-nvme-gen4-desempenho-e-eficiencia-para-upgrade-de-pc-snv3s-1000g</t>
+        </is>
+      </c>
+      <c r="I216" s="31" t="n">
+        <v>46313.53616898148</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="24" t="n">
+        <v>214</v>
+      </c>
+      <c r="B217" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="C217" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" s="32" t="n">
+        <v>2399</v>
+      </c>
+      <c r="E217" s="32" t="n">
+        <v>2090.79</v>
+      </c>
+      <c r="F217" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G217" s="25" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H217" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/464267/ssd-samsung-990-pro-1tb-nvme-m-2-2280-mz-v9p1t0b-am-</t>
+        </is>
+      </c>
+      <c r="I217" s="34" t="n">
+        <v>46313.5362037037</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="22" t="n">
+        <v>215</v>
+      </c>
+      <c r="B218" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C218" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" s="29" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="E218" s="29" t="n">
+        <v>533.78</v>
+      </c>
+      <c r="F218" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G218" s="23" t="inlineStr">
+        <is>
+          <t>Boa compra</t>
+        </is>
+      </c>
+      <c r="H218" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/781777/ssd-kingston-a400-480gb-sata-iii-2-5-leitura-500mb-s-gravacao-450mb-s-preto-sa400s37-480g</t>
+        </is>
+      </c>
+      <c r="I218" s="31" t="n">
+        <v>46313.53623842593</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="24" t="n">
+        <v>216</v>
+      </c>
+      <c r="B219" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="C219" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" s="32" t="n">
+        <v>759</v>
+      </c>
+      <c r="E219" s="32" t="n">
+        <v>762.13</v>
+      </c>
+      <c r="F219" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G219" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H219" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/172706/placa-mae-asus-tuf-gaming-b550m-plus-amd-am4-matx-ddr4-m-2-aura-para-fita-rgb-90mb14a0-c1bay0</t>
+        </is>
+      </c>
+      <c r="I219" s="34" t="n">
+        <v>46313.53627314815</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="22" t="n">
+        <v>217</v>
+      </c>
+      <c r="B220" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="C220" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" s="29" t="n">
+        <v>896.99</v>
+      </c>
+      <c r="E220" s="29" t="n">
+        <v>980.9</v>
+      </c>
+      <c r="F220" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G220" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H220" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/524346/placa-mae-msi-pro-b650m-p-amd-am5-m-atx-ddr5-pro-b650m-p</t>
+        </is>
+      </c>
+      <c r="I220" s="31" t="n">
+        <v>46313.53630787037</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="24" t="n">
+        <v>218</v>
+      </c>
+      <c r="B221" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="C221" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" s="32" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="E221" s="32" t="n">
+        <v>365.7</v>
+      </c>
+      <c r="F221" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G221" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H221" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/516056/fonte-corsair-cx-series-cx650-650w-80-plus-bronze-com-cabo-preto-cp-9020278-br</t>
+        </is>
+      </c>
+      <c r="I221" s="34" t="n">
+        <v>46313.53633101852</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="22" t="n">
+        <v>219</v>
+      </c>
+      <c r="B222" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C222" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" s="29" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="E222" s="29" t="n">
+        <v>294.45</v>
+      </c>
+      <c r="F222" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G222" s="23" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H222" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/369658/fonte-msi-mag-a650bn-650w-80-plus-bronze-pfc-ativo-com-cabo-preto-306-7zp2b22-ce0</t>
+        </is>
+      </c>
+      <c r="I222" s="31" t="n">
+        <v>46313.53636574074</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="24" t="n">
+        <v>220</v>
+      </c>
+      <c r="B223" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="C223" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" s="32" t="n">
+        <v>699.89</v>
+      </c>
+      <c r="E223" s="32" t="n">
+        <v>710.7</v>
+      </c>
+      <c r="F223" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G223" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H223" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/514895/fonte-xpg-core-reactor-ii-ve-750w-80-plus-gold-modular-pfc-ativo-preto-75261425</t>
+        </is>
+      </c>
+      <c r="I223" s="34" t="n">
+        <v>46313.53638888889</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="22" t="n">
+        <v>221</v>
+      </c>
+      <c r="B224" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C224" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D224" s="29" t="n">
+        <v>2729.99</v>
+      </c>
+      <c r="E224" s="29" t="n">
+        <v>2799.97</v>
+      </c>
+      <c r="F224" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G224" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H224" s="26" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/43432/placa-de-video-pcyes-nvidia-geforce-rtx-5060-8gb-gddr7-128bits-dual-fan-pvrtx5060b2f128</t>
+        </is>
+      </c>
+      <c r="I224" s="31" t="n">
+        <v>46313.53697916667</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="24" t="n">
+        <v>222</v>
+      </c>
+      <c r="B225" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C225" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D225" s="32" t="n">
+        <v>5599.99</v>
+      </c>
+      <c r="E225" s="32" t="n">
+        <v>5437.77</v>
+      </c>
+      <c r="F225" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G225" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H225" s="27" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/43330/placa-de-video-asus-nvidia-geforce-rtx-5070-ats-oc-v2-12gb-gddr7-dlss-ray-tracing-ats-rtx5070-o12g-v2</t>
+        </is>
+      </c>
+      <c r="I225" s="34" t="n">
+        <v>46313.53697916667</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="22" t="n">
+        <v>223</v>
+      </c>
+      <c r="B226" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C226" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D226" s="29" t="n">
+        <v>2499.99</v>
+      </c>
+      <c r="E226" s="29" t="n">
+        <v>2321.34</v>
+      </c>
+      <c r="F226" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G226" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H226" s="26" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/36876/placa-de-video-superframe-nvidia-geforce-rtx-3060-epic-especial-edition-white-12gb-gddr6-dlss-ray-tracing-sf-gc-spnv306012d6</t>
+        </is>
+      </c>
+      <c r="I226" s="31" t="n">
+        <v>46313.53697916667</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="24" t="n">
+        <v>224</v>
+      </c>
+      <c r="B227" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C227" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D227" s="32" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="E227" s="32" t="n">
+        <v>1964.96</v>
+      </c>
+      <c r="F227" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G227" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H227" s="27" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/43356/placa-de-video-biostar-amd-radeon-rx-7600-oc-ultimate-gaming-8gb-gddr6-fsr-ray-tracing-va76s6rm81</t>
+        </is>
+      </c>
+      <c r="I227" s="34" t="n">
+        <v>46313.53697916667</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="22" t="n">
+        <v>225</v>
+      </c>
+      <c r="B228" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="C228" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D228" s="29" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="E228" s="29" t="n">
+        <v>1055.21</v>
+      </c>
+      <c r="F228" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G228" s="23" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H228" s="26" t="inlineStr">
+        <is>
+          <t>https://www.pichau.com.br/ssd-kingston-nv3-1tb-m-2-2280-pcie-nvme-leitura-6000mb-s-gravacao-4000mb-s-snv3s-1000g</t>
+        </is>
+      </c>
+      <c r="I228" s="31" t="n">
+        <v>46313.54039351852</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="24" t="n">
+        <v>226</v>
+      </c>
+      <c r="B229" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C229" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D229" s="32" t="n">
+        <v>759.9</v>
+      </c>
+      <c r="E229" s="32" t="n">
+        <v>562.2</v>
+      </c>
+      <c r="F229" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G229" s="25" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H229" s="27" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/19314/memoria-kingston-fury-beast-8gb-3200mhz-ddr4-black-kf432c16bb8</t>
+        </is>
+      </c>
+      <c r="I229" s="34" t="n">
+        <v>46313.54103009259</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="22" t="n">
+        <v>227</v>
+      </c>
+      <c r="B230" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C230" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D230" s="29" t="n">
+        <v>788.5</v>
+      </c>
+      <c r="E230" s="29" t="n">
+        <v>819.6900000000001</v>
+      </c>
+      <c r="F230" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G230" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H230" s="26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0GKHVP14D</t>
+        </is>
+      </c>
+      <c r="I230" s="31" t="n">
+        <v>46313.54115740741</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="24" t="n">
+        <v>228</v>
+      </c>
+      <c r="B231" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C231" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D231" s="32" t="n">
+        <v>1006.05</v>
+      </c>
+      <c r="E231" s="32" t="n">
+        <v>1139.15</v>
+      </c>
+      <c r="F231" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G231" s="25" t="inlineStr">
+        <is>
+          <t>Boa compra</t>
+        </is>
+      </c>
+      <c r="H231" s="27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0C3T4MFMM</t>
+        </is>
+      </c>
+      <c r="I231" s="34" t="n">
+        <v>46313.54141203704</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="22" t="n">
+        <v>229</v>
+      </c>
+      <c r="B232" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C232" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D232" s="29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E232" s="29" t="n">
+        <v>1059.99</v>
+      </c>
+      <c r="F232" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G232" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H232" s="26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0BMQJWBDM</t>
+        </is>
+      </c>
+      <c r="I232" s="31" t="n">
+        <v>46313.54163194444</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="24" t="n">
+        <v>230</v>
+      </c>
+      <c r="B233" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C233" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D233" s="32" t="n">
+        <v>1999.99</v>
+      </c>
+      <c r="E233" s="32" t="n">
+        <v>1957.56</v>
+      </c>
+      <c r="F233" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G233" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H233" s="27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0BTZB7F88</t>
+        </is>
+      </c>
+      <c r="I233" s="34" t="n">
+        <v>46313.5418287037</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="22" t="n">
+        <v>231</v>
+      </c>
+      <c r="B234" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C234" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D234" s="29" t="n">
+        <v>1227.4</v>
+      </c>
+      <c r="E234" s="29" t="n">
+        <v>960.67</v>
+      </c>
+      <c r="F234" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G234" s="23" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H234" s="26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B09NPJRDGD</t>
+        </is>
+      </c>
+      <c r="I234" s="31" t="n">
+        <v>46313.54200231482</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="24" t="n">
+        <v>232</v>
+      </c>
+      <c r="B235" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C235" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D235" s="32" t="n">
+        <v>3752.5</v>
+      </c>
+      <c r="E235" s="32" t="n">
+        <v>1032.99</v>
+      </c>
+      <c r="F235" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G235" s="25" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H235" s="27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0HHTGGH51</t>
+        </is>
+      </c>
+      <c r="I235" s="34" t="n">
+        <v>46313.54222222222</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="22" t="n">
+        <v>233</v>
+      </c>
+      <c r="B236" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C236" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D236" s="29" t="n">
+        <v>2799.99</v>
+      </c>
+      <c r="E236" s="29" t="n">
+        <v>2799.97</v>
+      </c>
+      <c r="F236" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G236" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H236" s="26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B09729YMPT</t>
+        </is>
+      </c>
+      <c r="I236" s="31" t="n">
+        <v>46313.54240740741</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="24" t="n">
+        <v>234</v>
+      </c>
+      <c r="B237" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C237" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D237" s="32" t="n">
+        <v>5880.5</v>
+      </c>
+      <c r="E237" s="32" t="n">
+        <v>5437.77</v>
+      </c>
+      <c r="F237" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G237" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H237" s="27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0DYS9QRGT</t>
+        </is>
+      </c>
+      <c r="I237" s="34" t="n">
+        <v>46313.54261574074</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="22" t="n">
+        <v>235</v>
+      </c>
+      <c r="B238" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C238" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D238" s="29" t="n">
+        <v>2458.8</v>
+      </c>
+      <c r="E238" s="29" t="n">
+        <v>2321.34</v>
+      </c>
+      <c r="F238" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G238" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H238" s="26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0H378SSY3</t>
+        </is>
+      </c>
+      <c r="I238" s="31" t="n">
+        <v>46313.5428587963</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="24" t="n">
+        <v>236</v>
+      </c>
+      <c r="B239" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C239" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D239" s="32" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="E239" s="32" t="n">
+        <v>1964.96</v>
+      </c>
+      <c r="F239" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G239" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H239" s="27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0C626FFG2</t>
+        </is>
+      </c>
+      <c r="I239" s="34" t="n">
+        <v>46313.54304398148</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="22" t="n">
+        <v>237</v>
+      </c>
+      <c r="B240" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C240" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D240" s="29" t="n">
+        <v>398.71</v>
+      </c>
+      <c r="E240" s="29" t="n">
+        <v>562.2</v>
+      </c>
+      <c r="F240" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G240" s="23" t="inlineStr">
+        <is>
+          <t>Boa compra</t>
+        </is>
+      </c>
+      <c r="H240" s="26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B097K5J1SB</t>
+        </is>
+      </c>
+      <c r="I240" s="31" t="n">
+        <v>46313.54325231481</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="24" t="n">
+        <v>238</v>
+      </c>
+      <c r="B241" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C241" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D241" s="32" t="n">
+        <v>798.1900000000001</v>
+      </c>
+      <c r="E241" s="32" t="n">
+        <v>1041.41</v>
+      </c>
+      <c r="F241" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G241" s="25" t="inlineStr">
+        <is>
+          <t>Boa compra</t>
+        </is>
+      </c>
+      <c r="H241" s="27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B097K3WV9J</t>
+        </is>
+      </c>
+      <c r="I241" s="34" t="n">
+        <v>46313.54342592593</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="22" t="n">
+        <v>239</v>
+      </c>
+      <c r="B242" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="C242" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D242" s="29" t="n">
+        <v>947.15</v>
+      </c>
+      <c r="E242" s="29" t="n">
+        <v>1055.21</v>
+      </c>
+      <c r="F242" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G242" s="23" t="inlineStr">
+        <is>
+          <t>Boa compra</t>
+        </is>
+      </c>
+      <c r="H242" s="26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0DBR3DZWG</t>
+        </is>
+      </c>
+      <c r="I242" s="31" t="n">
+        <v>46313.54385416667</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="24" t="n">
+        <v>240</v>
+      </c>
+      <c r="B243" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="C243" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D243" s="32" t="n">
+        <v>1720.97</v>
+      </c>
+      <c r="E243" s="32" t="n">
+        <v>2090.79</v>
+      </c>
+      <c r="F243" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G243" s="25" t="inlineStr">
+        <is>
+          <t>Boa compra</t>
+        </is>
+      </c>
+      <c r="H243" s="27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0BHJF2VRN</t>
+        </is>
+      </c>
+      <c r="I243" s="34" t="n">
+        <v>46313.54403935185</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="22" t="n">
+        <v>241</v>
+      </c>
+      <c r="B244" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C244" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D244" s="29" t="n">
+        <v>615.6</v>
+      </c>
+      <c r="E244" s="29" t="n">
+        <v>533.78</v>
+      </c>
+      <c r="F244" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G244" s="23" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H244" s="26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B08NG86HZD</t>
+        </is>
+      </c>
+      <c r="I244" s="31" t="n">
+        <v>46313.54422453704</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="24" t="n">
+        <v>242</v>
+      </c>
+      <c r="B245" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="C245" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D245" s="32" t="n">
+        <v>1387.54</v>
+      </c>
+      <c r="E245" s="32" t="n">
+        <v>980.9</v>
+      </c>
+      <c r="F245" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G245" s="25" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H245" s="27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0FBT23ZY8</t>
+        </is>
+      </c>
+      <c r="I245" s="34" t="n">
+        <v>46313.54464120371</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="22" t="n">
+        <v>243</v>
+      </c>
+      <c r="B246" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C246" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D246" s="29" t="n">
+        <v>266.71</v>
+      </c>
+      <c r="E246" s="29" t="n">
+        <v>294.45</v>
+      </c>
+      <c r="F246" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G246" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H246" s="26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/dp/B0991TZ399</t>
+        </is>
+      </c>
+      <c r="I246" s="31" t="n">
+        <v>46313.54508101852</v>
       </c>
     </row>
   </sheetData>
@@ -8539,10 +9958,53 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId243"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId201"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId244"/>
   </tableParts>
 </worksheet>
 </file>
--- a/dados/banco_dados.xlsx
+++ b/dados/banco_dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="dicionario" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="produto" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="loja" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="oferta" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dicionario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="produto" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="loja" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oferta" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -335,8 +335,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tb_oferta" displayName="tb_oferta" ref="A3:I246" headerRowCount="1">
-  <autoFilter ref="A3:I246"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tb_oferta" displayName="tb_oferta" ref="A3:I272" headerRowCount="1">
+  <autoFilter ref="A3:I272"/>
   <tableColumns count="9">
     <tableColumn id="1" name="id_oferta"/>
     <tableColumn id="2" name="id_produto"/>
@@ -661,7 +661,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Modelo estrela do pipeline de preços · atualizado em 18/10/2026 13:05</t>
+          <t>Modelo estrela do pipeline de preços · atualizado em 19/10/2026 11:07</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I246"/>
+  <dimension ref="A1:I272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9751,6 +9751,864 @@
       </c>
       <c r="I246" s="31" t="n">
         <v>46313.54508101852</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="24" t="n">
+        <v>244</v>
+      </c>
+      <c r="B247" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C247" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D247" s="32" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="E247" s="32" t="n">
+        <v>1134.33</v>
+      </c>
+      <c r="F247" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G247" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H247" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/320797/processador-amd-ryzen-7-5700x-3-4ghz-4-6ghz-max-turbo-cache-36mb-8-nucleos-16-threads-am4-sem-video-integrado-100-100000926wof</t>
+        </is>
+      </c>
+      <c r="I247" s="34" t="n">
+        <v>46314.12506944445</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="22" t="n">
+        <v>245</v>
+      </c>
+      <c r="B248" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C248" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" s="29" t="n">
+        <v>1549.99</v>
+      </c>
+      <c r="E248" s="29" t="n">
+        <v>1054.54</v>
+      </c>
+      <c r="F248" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G248" s="23" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H248" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/405799/processador-amd-ryzen-5-7600-3-8ghz-5-1ghz-max-turbo-cache-38mb-6-nucleos-12-threads-am5-com-video-integrado-100-100001015box</t>
+        </is>
+      </c>
+      <c r="I248" s="31" t="n">
+        <v>46314.12511574074</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="24" t="n">
+        <v>246</v>
+      </c>
+      <c r="B249" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C249" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D249" s="32" t="n">
+        <v>1978.9</v>
+      </c>
+      <c r="E249" s="32" t="n">
+        <v>1962.47</v>
+      </c>
+      <c r="F249" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G249" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H249" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/466557/processador-amd-ryzen-7-7800x3d-4-2ghz-5-0ghz-max-turbo-cache-104mb-am5-c-video-e-sem-cooler-100-100000910wof</t>
+        </is>
+      </c>
+      <c r="I249" s="34" t="n">
+        <v>46314.12515046296</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="22" t="n">
+        <v>247</v>
+      </c>
+      <c r="B250" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C250" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" s="29" t="n">
+        <v>859.99</v>
+      </c>
+      <c r="E250" s="29" t="n">
+        <v>973.4400000000001</v>
+      </c>
+      <c r="F250" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G250" s="23" t="inlineStr">
+        <is>
+          <t>Boa compra</t>
+        </is>
+      </c>
+      <c r="H250" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/283718/processador-intel-core-i5-12400f-2-5ghz-4-4ghz-max-turbo-cache-18mb-6-nucleos-12-threads-lga-1700-sem-video-integrado-bx8071512400f</t>
+        </is>
+      </c>
+      <c r="I250" s="31" t="n">
+        <v>46314.12518518518</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="24" t="n">
+        <v>248</v>
+      </c>
+      <c r="B251" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C251" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D251" s="32" t="n">
+        <v>1069.99</v>
+      </c>
+      <c r="E251" s="32" t="n">
+        <v>1036.36</v>
+      </c>
+      <c r="F251" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G251" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H251" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/531209/processador-intel-core-i5-14400f-14-geracao-3-5-ghz-4-7-ghz-turbo-cache-20mb-10-nucleos-16-threads-lga1700-sem-video-integrado-bx8071514400f</t>
+        </is>
+      </c>
+      <c r="I251" s="34" t="n">
+        <v>46314.12520833333</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="22" t="n">
+        <v>249</v>
+      </c>
+      <c r="B252" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C252" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" s="29" t="n">
+        <v>2899.9</v>
+      </c>
+      <c r="E252" s="29" t="n">
+        <v>2802.28</v>
+      </c>
+      <c r="F252" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G252" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H252" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/903752/gpu-inno3d-geforce-rtx-5060-twin-x2-8gb-128bits-gddr7-n50602-08d7-195071n</t>
+        </is>
+      </c>
+      <c r="I252" s="31" t="n">
+        <v>46314.12524305555</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="24" t="n">
+        <v>250</v>
+      </c>
+      <c r="B253" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C253" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D253" s="32" t="n">
+        <v>5499.99</v>
+      </c>
+      <c r="E253" s="32" t="n">
+        <v>5489.09</v>
+      </c>
+      <c r="F253" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G253" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H253" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/989623/placa-de-video-palit-rtx-5070-infinity-3-nvidia-geforce-12gb-gddr7-192bit-3-dp-e-hdmi-ne75070019k9-gb2050s</t>
+        </is>
+      </c>
+      <c r="I253" s="34" t="n">
+        <v>46314.1252662037</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="22" t="n">
+        <v>251</v>
+      </c>
+      <c r="B254" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C254" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D254" s="29" t="n">
+        <v>2199.99</v>
+      </c>
+      <c r="E254" s="29" t="n">
+        <v>2336.32</v>
+      </c>
+      <c r="F254" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G254" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H254" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/996572/placa-de-video-husky-alpha-rtx-3060-nvidia-12gb-gddr6-192-bit-dual-fan-hdmi-3x-displayport-hvg023060</t>
+        </is>
+      </c>
+      <c r="I254" s="31" t="n">
+        <v>46314.1253125</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="24" t="n">
+        <v>252</v>
+      </c>
+      <c r="B255" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C255" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D255" s="32" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="E255" s="32" t="n">
+        <v>1951.04</v>
+      </c>
+      <c r="F255" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G255" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H255" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/459144/placa-de-video-rx-7600-challenger-asrock-amd-radeon-8gb-gddr6-90-ga41zz-00uanf</t>
+        </is>
+      </c>
+      <c r="I255" s="34" t="n">
+        <v>46314.12533564815</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="22" t="n">
+        <v>253</v>
+      </c>
+      <c r="B256" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C256" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D256" s="29" t="n">
+        <v>519.99</v>
+      </c>
+      <c r="E256" s="29" t="n">
+        <v>541.63</v>
+      </c>
+      <c r="F256" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G256" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H256" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/313833/memoria-kingston-fury-beast-8gb-3200mhz-ddr4-cl16-preto-kf432c16bb-8</t>
+        </is>
+      </c>
+      <c r="I256" s="31" t="n">
+        <v>46314.12537037037</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="24" t="n">
+        <v>254</v>
+      </c>
+      <c r="B257" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C257" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D257" s="32" t="n">
+        <v>1016.41</v>
+      </c>
+      <c r="E257" s="32" t="n">
+        <v>1005.95</v>
+      </c>
+      <c r="F257" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G257" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H257" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/938663/memoria-ram-kingston-hyperx-ddr4-16gb-2666mhz-cl16-udimm-desktop</t>
+        </is>
+      </c>
+      <c r="I257" s="34" t="n">
+        <v>46314.12539351852</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="22" t="n">
+        <v>255</v>
+      </c>
+      <c r="B258" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="C258" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D258" s="29" t="n">
+        <v>2049.99</v>
+      </c>
+      <c r="E258" s="29" t="n">
+        <v>2119.18</v>
+      </c>
+      <c r="F258" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G258" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H258" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/285967/memoria-ram-kingston-fury-beast-16gb-5600mhz-ddr5-cl40-para-intel-xmp-preto-kf556c40bb-16</t>
+        </is>
+      </c>
+      <c r="I258" s="31" t="n">
+        <v>46314.12542824074</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="24" t="n">
+        <v>256</v>
+      </c>
+      <c r="B259" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="C259" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" s="32" t="n">
+        <v>1139.05</v>
+      </c>
+      <c r="E259" s="32" t="n">
+        <v>1063.82</v>
+      </c>
+      <c r="F259" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G259" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H259" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/1021928/ssd-kingston-nv3-1tb-m-2-2280-nvme-gen4-desempenho-e-eficiencia-para-upgrade-de-pc-snv3s-1000g</t>
+        </is>
+      </c>
+      <c r="I259" s="34" t="n">
+        <v>46314.12545138889</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="22" t="n">
+        <v>257</v>
+      </c>
+      <c r="B260" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C260" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" s="29" t="n">
+        <v>2399</v>
+      </c>
+      <c r="E260" s="29" t="n">
+        <v>2085.19</v>
+      </c>
+      <c r="F260" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G260" s="23" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H260" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/464267/ssd-samsung-990-pro-1tb-nvme-m-2-2280-mz-v9p1t0b-am-</t>
+        </is>
+      </c>
+      <c r="I260" s="31" t="n">
+        <v>46314.12547453704</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="24" t="n">
+        <v>258</v>
+      </c>
+      <c r="B261" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="C261" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" s="32" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="E261" s="32" t="n">
+        <v>535.87</v>
+      </c>
+      <c r="F261" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G261" s="25" t="inlineStr">
+        <is>
+          <t>Boa compra</t>
+        </is>
+      </c>
+      <c r="H261" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/781777/ssd-kingston-a400-480gb-sata-iii-2-5-leitura-500mb-s-gravacao-450mb-s-preto-sa400s37-480g</t>
+        </is>
+      </c>
+      <c r="I261" s="34" t="n">
+        <v>46314.12550925926</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="22" t="n">
+        <v>259</v>
+      </c>
+      <c r="B262" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C262" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" s="29" t="n">
+        <v>759</v>
+      </c>
+      <c r="E262" s="29" t="n">
+        <v>761.6799999999999</v>
+      </c>
+      <c r="F262" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G262" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H262" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/172706/placa-mae-asus-tuf-gaming-b550m-plus-amd-am4-matx-ddr4-m-2-aura-para-fita-rgb-90mb14a0-c1bay0</t>
+        </is>
+      </c>
+      <c r="I262" s="31" t="n">
+        <v>46314.12553240741</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="24" t="n">
+        <v>260</v>
+      </c>
+      <c r="B263" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="C263" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" s="32" t="n">
+        <v>896.99</v>
+      </c>
+      <c r="E263" s="32" t="n">
+        <v>971.5700000000001</v>
+      </c>
+      <c r="F263" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G263" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H263" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/524346/placa-mae-msi-pro-b650m-p-amd-am5-m-atx-ddr5-pro-b650m-p</t>
+        </is>
+      </c>
+      <c r="I263" s="34" t="n">
+        <v>46314.12556712963</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="22" t="n">
+        <v>261</v>
+      </c>
+      <c r="B264" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C264" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" s="29" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="E264" s="29" t="n">
+        <v>364.99</v>
+      </c>
+      <c r="F264" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G264" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H264" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/516056/fonte-corsair-cx-series-cx650-650w-80-plus-bronze-com-cabo-preto-cp-9020278-br</t>
+        </is>
+      </c>
+      <c r="I264" s="31" t="n">
+        <v>46314.12560185185</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="24" t="n">
+        <v>262</v>
+      </c>
+      <c r="B265" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="C265" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D265" s="32" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="E265" s="32" t="n">
+        <v>296.98</v>
+      </c>
+      <c r="F265" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G265" s="25" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H265" s="27" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/369658/fonte-msi-mag-a650bn-650w-80-plus-bronze-pfc-ativo-com-cabo-preto-306-7zp2b22-ce0</t>
+        </is>
+      </c>
+      <c r="I265" s="34" t="n">
+        <v>46314.125625</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="22" t="n">
+        <v>263</v>
+      </c>
+      <c r="B266" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C266" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D266" s="29" t="n">
+        <v>699.89</v>
+      </c>
+      <c r="E266" s="29" t="n">
+        <v>708.9</v>
+      </c>
+      <c r="F266" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G266" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H266" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/514895/fonte-xpg-core-reactor-ii-ve-750w-80-plus-gold-modular-pfc-ativo-preto-75261425</t>
+        </is>
+      </c>
+      <c r="I266" s="31" t="n">
+        <v>46314.12564814815</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="24" t="n">
+        <v>264</v>
+      </c>
+      <c r="B267" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C267" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D267" s="32" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="E267" s="32" t="n">
+        <v>1134.33</v>
+      </c>
+      <c r="F267" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G267" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H267" s="27" t="inlineStr">
+        <is>
+          <t>https://www.pichau.com.br/processador-amd-ryzen-7-5700x-8-core-16-threads-3-4ghz-4-6ghz-turbo-cache-36mb-am4-100-100000926wof</t>
+        </is>
+      </c>
+      <c r="I267" s="34" t="n">
+        <v>46314.12577546296</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="22" t="n">
+        <v>265</v>
+      </c>
+      <c r="B268" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C268" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D268" s="29" t="n">
+        <v>1999.99</v>
+      </c>
+      <c r="E268" s="29" t="n">
+        <v>1962.47</v>
+      </c>
+      <c r="F268" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G268" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H268" s="26" t="inlineStr">
+        <is>
+          <t>https://www.pichau.com.br/processador-amd-ryzen-7-7800x3d-8-core-16-threads-4-2ghz-5-0ghzturbo-cache-104mb-am5-100-100000910wof</t>
+        </is>
+      </c>
+      <c r="I268" s="31" t="n">
+        <v>46314.12577546296</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="24" t="n">
+        <v>266</v>
+      </c>
+      <c r="B269" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="C269" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D269" s="32" t="n">
+        <v>1199.9</v>
+      </c>
+      <c r="E269" s="32" t="n">
+        <v>1063.82</v>
+      </c>
+      <c r="F269" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G269" s="25" t="inlineStr">
+        <is>
+          <t>Evitar</t>
+        </is>
+      </c>
+      <c r="H269" s="27" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/31564/ssd-kingston-nv3-1tb-m2-nvme-2280-pcie-40-leitura-6000mbs-e-gravacao-4000mbs-snv3s1000g</t>
+        </is>
+      </c>
+      <c r="I269" s="34" t="n">
+        <v>46314.12585648148</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="22" t="n">
+        <v>267</v>
+      </c>
+      <c r="B270" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C270" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D270" s="29" t="n">
+        <v>569.9</v>
+      </c>
+      <c r="E270" s="29" t="n">
+        <v>535.87</v>
+      </c>
+      <c r="F270" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G270" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H270" s="26" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/19382/ssd-kingston-a400-480gb-sata-iii-leitura-500mbs-gravacao-450mbs-sa400s37480g-imp</t>
+        </is>
+      </c>
+      <c r="I270" s="31" t="n">
+        <v>46314.12585648148</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="24" t="n">
+        <v>268</v>
+      </c>
+      <c r="B271" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C271" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D271" s="32" t="n">
+        <v>1959.99</v>
+      </c>
+      <c r="E271" s="32" t="n">
+        <v>1951.04</v>
+      </c>
+      <c r="F271" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G271" s="25" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H271" s="27" t="inlineStr">
+        <is>
+          <t>https://www.pichau.com.br/placa-de-video-powercolor-radeon-rx-7600-fighter-8gb-gddr6-128-bit-rx7600-8g-f-v2</t>
+        </is>
+      </c>
+      <c r="I271" s="34" t="n">
+        <v>46314.46310185185</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="22" t="n">
+        <v>269</v>
+      </c>
+      <c r="B272" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C272" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D272" s="29" t="n">
+        <v>779.99</v>
+      </c>
+      <c r="E272" s="29" t="n">
+        <v>761.6799999999999</v>
+      </c>
+      <c r="F272" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G272" s="23" t="inlineStr">
+        <is>
+          <t>Preço médio</t>
+        </is>
+      </c>
+      <c r="H272" s="26" t="inlineStr">
+        <is>
+          <t>https://www.terabyteshop.com.br/produto/13983/placa-mae-asus-tuf-gaming-b550m-plus-chipset-b550-amd-am4-matx-ddr4</t>
+        </is>
+      </c>
+      <c r="I272" s="31" t="n">
+        <v>46314.46341435185</v>
       </c>
     </row>
   </sheetData>
@@ -10001,10 +10859,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId269"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId244"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId270"/>
   </tableParts>
 </worksheet>
 </file>